--- a/Data/FlightPlan/FPL_24AUG26.xlsx
+++ b/Data/FlightPlan/FPL_24AUG26.xlsx
@@ -242,7 +242,7 @@
     <t>10:20</t>
   </si>
   <si>
-    <t>09:45</t>
+    <t>10:28</t>
   </si>
   <si>
     <t>16:10</t>
@@ -395,162 +395,171 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>07:44</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
     <t>13:50</t>
   </si>
   <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>07:44</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:04</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:14</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>10:23</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
     <t>15:25</t>
   </si>
   <si>
@@ -578,6 +587,9 @@
     <t>CGK</t>
   </si>
   <si>
+    <t>12:38</t>
+  </si>
+  <si>
     <t>16:40</t>
   </si>
   <si>
@@ -716,238 +728,250 @@
     <t>09:10</t>
   </si>
   <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>06:51</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>7614D</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>7615 *</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>08:47</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>08:22</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:32</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:28</t>
+  </si>
+  <si>
     <t>11:15</t>
   </si>
   <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>06:51</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>7614D</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>08:54</t>
-  </si>
-  <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>09:19</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>08:47</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>08:22</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:32</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>08:28</t>
-  </si>
-  <si>
-    <t>11:08</t>
+    <t>11:14</t>
   </si>
   <si>
     <t>12:10</t>
@@ -968,6 +992,9 @@
     <t>VN-A636</t>
   </si>
   <si>
+    <t>09:13</t>
+  </si>
+  <si>
     <t>10:45</t>
   </si>
   <si>
@@ -995,7 +1022,7 @@
     <t>06:53</t>
   </si>
   <si>
-    <t>10:50</t>
+    <t>10:22</t>
   </si>
   <si>
     <t>16:05</t>
@@ -1016,6 +1043,9 @@
     <t>08:37</t>
   </si>
   <si>
+    <t>10:32</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1115,6 +1145,9 @@
     <t>08:49</t>
   </si>
   <si>
+    <t>11:52</t>
+  </si>
+  <si>
     <t>20:10</t>
   </si>
   <si>
@@ -1148,6 +1181,9 @@
     <t>08:34</t>
   </si>
   <si>
+    <t>10:44</t>
+  </si>
+  <si>
     <t>18:30</t>
   </si>
   <si>
@@ -1181,7 +1217,7 @@
     <t>VN-A661</t>
   </si>
   <si>
-    <t>11:07</t>
+    <t>10:54</t>
   </si>
   <si>
     <t>23:55</t>
@@ -1217,6 +1253,9 @@
     <t>08:43</t>
   </si>
   <si>
+    <t>11:27</t>
+  </si>
+  <si>
     <t>VN-A668</t>
   </si>
   <si>
@@ -1232,9 +1271,6 @@
     <t>08:05</t>
   </si>
   <si>
-    <t>10:22</t>
-  </si>
-  <si>
     <t>VN-A670</t>
   </si>
   <si>
@@ -1274,6 +1310,9 @@
     <t>06:41</t>
   </si>
   <si>
+    <t>10:26</t>
+  </si>
+  <si>
     <t>VN-A676</t>
   </si>
   <si>
@@ -1304,6 +1343,9 @@
     <t>VN-A685</t>
   </si>
   <si>
+    <t>10:39</t>
+  </si>
+  <si>
     <t>VN-A687</t>
   </si>
   <si>
@@ -1391,7 +1433,7 @@
     <t>Total Record(s): 393</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 24, 2026 09:09</t>
+    <t xml:space="preserve">Generated on  Aug 24, 2026 09:45</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3726,7 +3768,9 @@
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
+      <c t="s" r="M66" s="7">
+        <v>133</v>
+      </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c t="s" r="A67" s="6">
@@ -3752,7 +3796,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>105</v>
@@ -3782,7 +3826,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I68" s="7">
         <v>110</v>
@@ -3812,7 +3856,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>40</v>
@@ -3821,7 +3865,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3851,10 +3895,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3914,10 +3958,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>65</v>
@@ -3953,7 +3997,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3965,7 +4009,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>131</v>
@@ -3973,7 +4017,7 @@
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -3988,7 +4032,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3997,17 +4041,19 @@
         <v>74</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>86</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
+      <c t="s" r="M75" s="7">
+        <v>146</v>
+      </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c t="s" r="A76" s="6">
@@ -4021,22 +4067,22 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4054,7 +4100,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4066,10 +4112,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4087,7 +4133,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4102,7 +4148,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4135,7 +4181,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4144,18 +4190,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4170,27 +4216,27 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4205,7 +4251,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4214,7 +4260,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="I82" s="7">
         <v>44</v>
@@ -4238,13 +4284,13 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>40</v>
@@ -4271,7 +4317,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4280,13 +4326,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I84" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4304,19 +4350,19 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>33</v>
@@ -4337,7 +4383,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4346,13 +4392,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4370,13 +4416,13 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>40</v>
@@ -4418,7 +4464,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4430,15 +4476,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4453,7 +4499,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4468,7 +4514,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4486,7 +4532,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4498,7 +4544,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>92</v>
@@ -4534,7 +4580,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4546,15 +4592,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4569,7 +4615,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4581,15 +4627,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4604,7 +4650,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4619,14 +4665,14 @@
         <v>57</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="K95" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4641,7 +4687,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4656,7 +4702,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="K96" s="7">
         <v>28</v>
@@ -4678,7 +4724,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4687,13 +4733,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4711,22 +4757,22 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4744,7 +4790,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4756,10 +4802,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4777,7 +4823,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4789,10 +4835,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4825,7 +4871,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4834,13 +4880,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4858,13 +4904,13 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>17</v>
@@ -4906,7 +4952,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4915,7 +4961,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="I105" s="7">
         <v>119</v>
@@ -4925,7 +4971,9 @@
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
+      <c t="s" r="M105" s="7">
+        <v>192</v>
+      </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c t="s" r="A106" s="6">
@@ -4939,13 +4987,13 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>17</v>
@@ -4954,7 +5002,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4972,7 +5020,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4981,13 +5029,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5005,13 +5053,13 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>17</v>
@@ -5020,7 +5068,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5053,7 +5101,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5065,7 +5113,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>83</v>
@@ -5073,7 +5121,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5088,7 +5136,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5100,7 +5148,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>76</v>
@@ -5108,7 +5156,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5123,7 +5171,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5156,7 +5204,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5165,13 +5213,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5189,19 +5237,19 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>25</v>
@@ -5222,7 +5270,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5234,10 +5282,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5270,7 +5318,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5282,15 +5330,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5305,7 +5353,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5317,10 +5365,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5338,7 +5386,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5347,13 +5395,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5371,13 +5419,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>17</v>
@@ -5386,7 +5434,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5404,7 +5452,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5413,10 +5461,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>124</v>
@@ -5437,22 +5485,22 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5485,7 +5533,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5497,17 +5545,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>86</v>
       </c>
       <c t="s" r="K124" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5522,7 +5570,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5540,7 +5588,7 @@
         <v>122</v>
       </c>
       <c t="s" r="K125" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
@@ -5559,7 +5607,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5568,20 +5616,20 @@
         <v>40</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>51</v>
       </c>
       <c t="s" r="K126" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5596,13 +5644,13 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>40</v>
@@ -5611,10 +5659,10 @@
         <v>89</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="K127" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
@@ -5648,7 +5696,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5660,7 +5708,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>95</v>
@@ -5668,7 +5716,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5683,7 +5731,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5692,7 +5740,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>76</v>
@@ -5716,13 +5764,13 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>40</v>
@@ -5749,7 +5797,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5758,13 +5806,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5782,13 +5830,13 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>40</v>
@@ -5797,7 +5845,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5815,7 +5863,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5827,10 +5875,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5863,7 +5911,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5878,7 +5926,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5898,7 +5946,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5907,7 +5955,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I137" s="7">
         <v>87</v>
@@ -5931,22 +5979,22 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5964,7 +6012,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5976,10 +6024,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6012,7 +6060,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6021,20 +6069,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="K141" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6049,22 +6097,22 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6082,7 +6130,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6091,13 +6139,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6115,22 +6163,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6163,7 +6211,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6172,18 +6220,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6198,19 +6246,19 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>18</v>
@@ -6218,7 +6266,7 @@
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6233,7 +6281,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6242,13 +6290,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6266,19 +6314,19 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>122</v>
@@ -6299,7 +6347,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6311,7 +6359,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>51</v>
@@ -6332,7 +6380,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6347,7 +6395,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6365,7 +6413,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6377,10 +6425,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6413,7 +6461,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6425,7 +6473,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>38</v>
@@ -6433,7 +6481,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6448,7 +6496,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6460,15 +6508,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6483,7 +6531,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6495,10 +6543,10 @@
         <v>106</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6516,7 +6564,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6549,7 +6597,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6558,13 +6606,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6582,22 +6630,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6630,27 +6678,27 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6665,7 +6713,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6674,20 +6722,20 @@
         <v>40</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="K162" s="7">
         <v>20</v>
       </c>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6702,22 +6750,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6750,7 +6798,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6759,18 +6807,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -6785,13 +6833,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>74</v>
@@ -6805,7 +6853,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6820,7 +6868,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6829,13 +6877,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6853,22 +6901,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6886,7 +6934,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6895,10 +6943,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>48</v>
@@ -6919,22 +6967,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6952,19 +7000,19 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>52</v>
@@ -6985,13 +7033,13 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>74</v>
@@ -7018,7 +7066,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7030,10 +7078,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7059,26 +7107,26 @@
         <v>13</v>
       </c>
       <c t="s" r="B175" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>72</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>93</v>
@@ -7086,44 +7134,44 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c t="s" r="A176" s="6">
-        <v>13</v>
-      </c>
-      <c r="B176" s="7">
-        <v>7615</v>
+        <v>35</v>
+      </c>
+      <c t="s" r="B176" s="7">
+        <v>279</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>72</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="K176" s="7">
-        <v>92</v>
+        <v>280</v>
       </c>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7153,13 +7201,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>17</v>
@@ -7172,7 +7220,9 @@
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
-      <c r="M178" s="7"/>
+      <c t="s" r="M178" s="7">
+        <v>283</v>
+      </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c t="s" r="A179" s="6">
@@ -7186,7 +7236,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7198,10 +7248,10 @@
         <v>85</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7219,7 +7269,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7231,7 +7281,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>54</v>
@@ -7252,7 +7302,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7264,7 +7314,7 @@
         <v>67</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>65</v>
@@ -7300,7 +7350,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7309,18 +7359,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7335,22 +7385,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7368,19 +7418,19 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>79</v>
@@ -7401,13 +7451,13 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
@@ -7434,7 +7484,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7443,13 +7493,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7467,22 +7517,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7515,7 +7565,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7527,7 +7577,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>75</v>
@@ -7535,7 +7585,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7550,7 +7600,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7569,7 +7619,9 @@
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
-      <c r="M191" s="7"/>
+      <c t="s" r="M191" s="7">
+        <v>297</v>
+      </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c t="s" r="A192" s="6">
@@ -7583,7 +7635,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7592,13 +7644,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7616,19 +7668,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>62</v>
@@ -7649,7 +7701,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7658,13 +7710,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7682,22 +7734,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7730,7 +7782,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7742,15 +7794,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7765,7 +7817,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7774,17 +7826,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
-      <c r="M198" s="7"/>
+      <c t="s" r="M198" s="7">
+        <v>307</v>
+      </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c t="s" r="A199" s="6">
@@ -7798,13 +7852,13 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>17</v>
@@ -7813,7 +7867,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7831,7 +7885,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7843,7 +7897,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>25</v>
@@ -7864,7 +7918,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7876,10 +7930,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7897,7 +7951,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7906,13 +7960,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7930,19 +7984,19 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>92</v>
@@ -7978,7 +8032,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7987,10 +8041,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>119</v>
@@ -7998,7 +8052,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8013,22 +8067,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I206" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8046,22 +8100,22 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8094,7 +8148,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8109,12 +8163,12 @@
         <v>114</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8129,7 +8183,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8141,15 +8195,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8164,7 +8218,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8176,7 +8230,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>107</v>
@@ -8197,7 +8251,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8209,10 +8263,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8230,7 +8284,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8239,10 +8293,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>123</v>
@@ -8263,22 +8317,22 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8311,7 +8365,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8331,7 +8385,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8346,7 +8400,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8355,17 +8409,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>28</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
-      <c r="M217" s="7"/>
+      <c t="s" r="M217" s="7">
+        <v>166</v>
+      </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c t="s" r="A218" s="6">
@@ -8379,19 +8435,19 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>20</v>
@@ -8412,7 +8468,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8421,13 +8477,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8445,13 +8501,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>40</v>
@@ -8460,7 +8516,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8493,7 +8549,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8505,14 +8561,16 @@
         <v>74</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
-      <c r="M222" s="7"/>
+      <c t="s" r="M222" s="7">
+        <v>327</v>
+      </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c t="s" r="A223" s="6">
@@ -8526,7 +8584,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8541,7 +8599,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8559,7 +8617,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8574,7 +8632,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8592,7 +8650,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8604,10 +8662,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8625,7 +8683,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8637,10 +8695,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8658,7 +8716,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8670,10 +8728,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8691,7 +8749,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8706,7 +8764,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8724,7 +8782,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8739,7 +8797,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8757,7 +8815,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8769,7 +8827,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>83</v>
@@ -8805,7 +8863,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8817,15 +8875,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8840,7 +8898,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8852,14 +8910,16 @@
         <v>21</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
-      <c r="M233" s="7"/>
+      <c t="s" r="M233" s="7">
+        <v>337</v>
+      </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c t="s" r="A234" s="6">
@@ -8873,7 +8933,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8885,10 +8945,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>328</v>
+        <v>133</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8906,7 +8966,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8915,7 +8975,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I235" s="7">
         <v>122</v>
@@ -8939,22 +8999,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8972,7 +9032,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8981,13 +9041,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9005,13 +9065,13 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>17</v>
@@ -9053,7 +9113,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9062,18 +9122,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9088,16 +9148,16 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>41</v>
@@ -9108,7 +9168,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9123,26 +9183,28 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
-      <c r="M242" s="7"/>
+      <c t="s" r="M242" s="7">
+        <v>344</v>
+      </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c t="s" r="A243" s="6">
@@ -9156,13 +9218,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
@@ -9189,7 +9251,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9198,7 +9260,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>87</v>
@@ -9222,22 +9284,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9255,7 +9317,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9267,7 +9329,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>63</v>
@@ -9288,7 +9350,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9336,7 +9398,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9345,17 +9407,19 @@
         <v>36</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>127</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
-      <c r="M249" s="7"/>
+      <c t="s" r="M249" s="7">
+        <v>209</v>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1">
       <c t="s" r="A250" s="6">
@@ -9369,16 +9433,16 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>47</v>
@@ -9406,16 +9470,16 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>61</v>
@@ -9443,22 +9507,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9491,7 +9555,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9503,10 +9567,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9524,7 +9588,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9536,7 +9600,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>49</v>
@@ -9557,7 +9621,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9569,10 +9633,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9590,7 +9654,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9602,7 +9666,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>53</v>
@@ -9638,7 +9702,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9647,13 +9711,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9673,27 +9737,27 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9708,7 +9772,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9720,10 +9784,10 @@
         <v>85</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9741,7 +9805,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9753,10 +9817,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9774,7 +9838,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9783,10 +9847,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>123</v>
@@ -9807,19 +9871,19 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>52</v>
@@ -9840,7 +9904,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9852,10 +9916,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9873,7 +9937,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9885,10 +9949,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9921,7 +9985,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9930,18 +9994,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -9956,27 +10020,27 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>347</v>
+        <v>357</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -9991,7 +10055,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10000,13 +10064,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10024,19 +10088,19 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>70</v>
@@ -10057,7 +10121,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10069,10 +10133,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10105,7 +10169,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10114,18 +10178,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10140,19 +10204,19 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>110</v>
@@ -10173,7 +10237,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10182,13 +10246,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10206,22 +10270,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10254,7 +10318,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10263,18 +10327,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10289,13 +10353,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>17</v>
@@ -10304,7 +10368,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10322,7 +10386,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10334,7 +10398,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>118</v>
@@ -10370,7 +10434,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10382,7 +10446,7 @@
         <v>121</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>28</v>
@@ -10390,7 +10454,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10405,7 +10469,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10417,7 +10481,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>48</v>
@@ -10438,7 +10502,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10447,13 +10511,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10471,13 +10535,13 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>17</v>
@@ -10486,7 +10550,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10519,7 +10583,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10531,15 +10595,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10554,7 +10618,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10569,10 +10633,10 @@
         <v>95</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c t="s" r="K289" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
@@ -10591,7 +10655,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10600,16 +10664,16 @@
         <v>17</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c t="s" r="K290" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
@@ -10628,13 +10692,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>17</v>
@@ -10643,10 +10707,10 @@
         <v>47</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c t="s" r="K291" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
@@ -10665,7 +10729,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10674,13 +10738,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10698,22 +10762,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10731,7 +10795,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10746,7 +10810,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10764,7 +10828,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10776,10 +10840,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10812,7 +10876,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10821,10 +10885,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>119</v>
@@ -10832,7 +10896,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10847,19 +10911,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>86</v>
@@ -10880,7 +10944,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10889,10 +10953,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>20</v>
@@ -10913,22 +10977,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10946,7 +11010,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10955,7 +11019,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>51</v>
@@ -10979,22 +11043,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11027,7 +11091,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11036,10 +11100,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>95</v>
@@ -11047,7 +11111,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11062,13 +11126,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>40</v>
@@ -11081,7 +11145,9 @@
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
-      <c r="M305" s="7"/>
+      <c t="s" r="M305" s="7">
+        <v>378</v>
+      </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
       <c t="s" r="A306" s="6">
@@ -11095,7 +11161,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11110,7 +11176,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11128,7 +11194,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11140,7 +11206,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>25</v>
@@ -11161,7 +11227,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11170,13 +11236,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11194,22 +11260,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11242,7 +11308,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11254,15 +11320,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11277,7 +11343,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11289,14 +11355,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
-      <c r="M312" s="7"/>
+      <c t="s" r="M312" s="7">
+        <v>239</v>
+      </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
       <c t="s" r="A313" s="6">
@@ -11310,7 +11378,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11319,13 +11387,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11343,22 +11411,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11391,7 +11459,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11400,18 +11468,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11426,13 +11494,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>17</v>
@@ -11446,7 +11514,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11461,7 +11529,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11470,17 +11538,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>390</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c t="s" r="A319" s="6">
@@ -11494,13 +11564,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
@@ -11527,7 +11597,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11560,7 +11630,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11572,10 +11642,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11608,7 +11678,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11617,18 +11687,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11643,13 +11713,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>17</v>
@@ -11663,7 +11733,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -11678,7 +11748,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11687,7 +11757,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>132</v>
@@ -11711,22 +11781,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11744,7 +11814,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11756,7 +11826,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>32</v>
@@ -11777,7 +11847,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11810,7 +11880,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11822,10 +11892,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11858,7 +11928,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11867,13 +11937,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11893,27 +11963,27 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -11928,7 +11998,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11937,13 +12007,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11961,13 +12031,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>40</v>
@@ -11976,7 +12046,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11994,7 +12064,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12003,13 +12073,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12027,22 +12097,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12075,7 +12145,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12084,18 +12154,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>75</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12110,22 +12180,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12143,22 +12213,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12176,22 +12246,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12209,22 +12279,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12242,22 +12312,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12290,7 +12360,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12302,15 +12372,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12325,7 +12395,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12337,15 +12407,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>328</v>
+        <v>133</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12360,7 +12430,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12369,10 +12439,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>127</v>
@@ -12393,22 +12463,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12426,7 +12496,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12438,10 +12508,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12459,7 +12529,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12474,7 +12544,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12507,7 +12577,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12519,15 +12589,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12542,7 +12612,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12554,10 +12624,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12575,7 +12645,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12590,7 +12660,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12608,7 +12678,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12620,7 +12690,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>79</v>
@@ -12656,7 +12726,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12665,18 +12735,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12691,13 +12761,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>17</v>
@@ -12710,7 +12780,9 @@
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
-      <c r="M358" s="7"/>
+      <c t="s" r="M358" s="7">
+        <v>414</v>
+      </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c t="s" r="A359" s="6">
@@ -12724,7 +12796,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12757,7 +12829,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12805,7 +12877,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12817,15 +12889,15 @@
         <v>85</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12840,7 +12912,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12852,7 +12924,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>19</v>
@@ -12873,7 +12945,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12882,7 +12954,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I364" s="7">
         <v>122</v>
@@ -12906,22 +12978,22 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12939,7 +13011,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12948,13 +13020,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12972,22 +13044,22 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13020,7 +13092,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13029,10 +13101,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>117</v>
@@ -13040,7 +13112,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>405</v>
+        <v>418</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13055,27 +13127,27 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>407</v>
+        <v>337</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13090,7 +13162,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13123,7 +13195,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13135,10 +13207,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13156,7 +13228,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13204,7 +13276,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13216,15 +13288,15 @@
         <v>40</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13239,7 +13311,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13251,7 +13323,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>47</v>
@@ -13272,7 +13344,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13287,7 +13359,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13305,7 +13377,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13314,13 +13386,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13338,19 +13410,19 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>102</v>
@@ -13371,7 +13443,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13383,10 +13455,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13419,7 +13491,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13434,11 +13506,13 @@
         <v>126</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>328</v>
+        <v>133</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
-      <c r="M382" s="7"/>
+      <c t="s" r="M382" s="7">
+        <v>134</v>
+      </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
       <c t="s" r="A383" s="6">
@@ -13452,7 +13526,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13464,7 +13538,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>107</v>
@@ -13485,7 +13559,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13497,10 +13571,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13518,7 +13592,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13551,7 +13625,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13563,10 +13637,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13599,7 +13673,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13611,10 +13685,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13634,7 +13708,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13643,10 +13717,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>48</v>
@@ -13667,13 +13741,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>74</v>
@@ -13682,7 +13756,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13700,7 +13774,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13709,13 +13783,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13733,22 +13807,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13781,7 +13855,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13790,18 +13864,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>420</v>
+        <v>432</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -13816,27 +13890,27 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -13851,7 +13925,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13863,15 +13937,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>203</v>
+        <v>433</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -13886,7 +13960,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13898,10 +13972,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13919,7 +13993,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13928,13 +14002,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13952,22 +14026,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13985,7 +14059,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13994,10 +14068,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>25</v>
@@ -14018,22 +14092,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14051,7 +14125,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -14063,7 +14137,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>26</v>
@@ -14099,7 +14173,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -14108,18 +14182,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I404" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14134,16 +14208,16 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>76</v>
@@ -14167,22 +14241,22 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14200,13 +14274,13 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>40</v>
@@ -14233,7 +14307,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14245,10 +14319,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14266,7 +14340,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -14278,10 +14352,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14299,7 +14373,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14308,10 +14382,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>18</v>
@@ -14347,7 +14421,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14359,14 +14433,16 @@
         <v>40</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>127</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
-      <c r="M412" s="7"/>
+      <c t="s" r="M412" s="7">
+        <v>217</v>
+      </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
       <c t="s" r="A413" s="6">
@@ -14380,7 +14456,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14389,13 +14465,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14413,19 +14489,19 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>101</v>
@@ -14446,7 +14522,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14455,10 +14531,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>26</v>
@@ -14479,22 +14555,22 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14527,7 +14603,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14536,13 +14612,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14560,13 +14636,13 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>40</v>
@@ -14575,7 +14651,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14593,7 +14669,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14605,10 +14681,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14626,7 +14702,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14638,10 +14714,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14659,7 +14735,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14674,7 +14750,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14707,7 +14783,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14727,7 +14803,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -14742,7 +14818,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14761,7 +14837,9 @@
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
-      <c r="M425" s="7"/>
+      <c t="s" r="M425" s="7">
+        <v>444</v>
+      </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
       <c t="s" r="A426" s="6">
@@ -14775,7 +14853,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14787,10 +14865,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14808,7 +14886,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14823,7 +14901,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14856,7 +14934,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14865,18 +14943,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -14891,13 +14969,13 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>17</v>
@@ -14906,12 +14984,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>347</v>
+        <v>357</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -14926,7 +15004,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -14938,10 +15016,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14959,7 +15037,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -14971,7 +15049,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>87</v>
@@ -14992,7 +15070,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15007,7 +15085,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15025,7 +15103,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15037,7 +15115,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>61</v>
@@ -15073,7 +15151,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
@@ -15085,15 +15163,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15108,7 +15186,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
@@ -15120,17 +15198,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c t="s" r="K437" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15145,7 +15223,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -15160,14 +15238,14 @@
         <v>105</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="K438" s="7">
         <v>96</v>
       </c>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15182,7 +15260,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -15194,10 +15272,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -15230,7 +15308,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15239,17 +15317,19 @@
         <v>40</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>19</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
-      <c r="M441" s="7"/>
+      <c t="s" r="M441" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
       <c t="s" r="A442" s="6">
@@ -15263,13 +15343,13 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>40</v>
@@ -15278,7 +15358,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15296,7 +15376,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15344,7 +15424,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -15353,18 +15433,18 @@
         <v>40</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -15379,13 +15459,13 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>40</v>
@@ -15394,14 +15474,14 @@
         <v>57</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c t="s" r="K446" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15416,7 +15496,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15428,17 +15508,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>47</v>
       </c>
       <c t="s" r="K447" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15453,7 +15533,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15465,17 +15545,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c t="s" r="K448" s="7">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -15490,7 +15570,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15502,10 +15582,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="K449" s="7">
         <v>123</v>
@@ -15527,7 +15607,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -15539,17 +15619,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c t="s" r="K450" s="7">
         <v>124</v>
       </c>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -15579,7 +15659,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -15588,7 +15668,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>83</v>
@@ -15614,29 +15694,29 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>328</v>
+        <v>133</v>
       </c>
       <c t="s" r="K453" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -15651,7 +15731,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -15663,17 +15743,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="K454" s="7">
         <v>45</v>
       </c>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -15688,7 +15768,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -15700,17 +15780,17 @@
         <v>40</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="K455" s="7">
         <v>20</v>
       </c>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -15725,7 +15805,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -15734,13 +15814,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H456" s="8">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15758,22 +15838,22 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G457" s="8">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="H457" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15806,27 +15886,27 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c t="s" r="I459" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>442</v>
+        <v>456</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -15841,22 +15921,22 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15889,27 +15969,27 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -15924,7 +16004,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -15933,7 +16013,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I463" s="7">
         <v>25</v>
@@ -15957,22 +16037,22 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H464" s="8">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -16005,27 +16085,27 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -16040,22 +16120,22 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -16088,19 +16168,19 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H469" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>95</v>
@@ -16108,7 +16188,7 @@
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -16123,7 +16203,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -16132,10 +16212,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c t="s" r="J470" s="7">
         <v>102</v>
@@ -16156,22 +16236,22 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -16204,7 +16284,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
@@ -16213,13 +16293,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c t="s" r="I473" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16237,13 +16317,13 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G474" s="8">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c t="s" r="H474" s="8">
         <v>74</v>
@@ -16252,7 +16332,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -16285,7 +16365,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
@@ -16294,13 +16374,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c t="s" r="I476" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
@@ -16318,13 +16398,13 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G477" s="8">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c t="s" r="H477" s="8">
         <v>17</v>
@@ -16333,7 +16413,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
@@ -16341,7 +16421,7 @@
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c t="s" r="A478" s="9">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
@@ -16361,7 +16441,7 @@
     <row r="479" ht="65.25" customHeight="1"/>
     <row r="480" ht="17.25" customHeight="1">
       <c t="s" r="A480" s="10">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="B480" s="10"/>
       <c r="C480" s="10"/>
@@ -16374,7 +16454,7 @@
       <c r="J480" s="10"/>
       <c r="K480" s="10"/>
       <c t="s" r="L480" s="11">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="M480" s="11"/>
       <c r="N480" s="11"/>
